--- a/ai_logs/NTDanh_AI_log.xlsx
+++ b/ai_logs/NTDanh_AI_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUM2026\LAB211\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUM2026\LAB211\cloneProject\LAb211-Group3\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBA755A-574B-4E44-91D5-0C6330924939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C22FF8F-7DB5-4EE8-9C31-EC724241B9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="157">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -357,18 +357,6 @@
   </si>
   <si>
     <t>Fabrication</t>
-  </si>
-  <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -1073,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1710,24 +1698,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1893,18 +1869,18 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1912,54 +1888,54 @@
         <v>104</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1960,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1992,7 +1968,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -2000,185 +1976,185 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -2186,13 +2162,13 @@
         <v>46</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">

--- a/ai_logs/NTDanh_AI_log.xlsx
+++ b/ai_logs/NTDanh_AI_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUM2026\LAB211\cloneProject\LAb211-Group3\ai_logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUM2026\LAB211\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C22FF8F-7DB5-4EE8-9C31-EC724241B9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAB2725-3C5C-446D-90D9-B7E57B24CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="160">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -63,21 +63,18 @@
     <t>Assignment:</t>
   </si>
   <si>
+    <t>E-Commerce Flash Sale Simulation</t>
+  </si>
+  <si>
     <t>AI USAGE SUMMARY</t>
   </si>
   <si>
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>[e.g., ~150]</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
-    <t>[e.g., 18]</t>
-  </si>
-  <si>
     <t>Selection Ratio:</t>
   </si>
   <si>
@@ -87,7 +84,7 @@
     <t>Hallucination Detected:</t>
   </si>
   <si>
-    <t>[Count]</t>
+    <t>4</t>
   </si>
   <si>
     <t>AI TOOLS USED</t>
@@ -108,13 +105,13 @@
     <t>ChatGPT</t>
   </si>
   <si>
-    <t>Gemini</t>
-  </si>
-  <si>
-    <t>Gemini 1.5 Pro</t>
-  </si>
-  <si>
-    <t>Idea Generation / Learning</t>
+    <t>Gemini / ChatGPT</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>Idea Generation, Problem Solving, Code Review</t>
   </si>
   <si>
     <t>Claude</t>
@@ -201,135 +198,142 @@
     <t>001</t>
   </si>
   <si>
-    <t>PROBLEM-SOLVING</t>
-  </si>
-  <si>
-    <t>System Analysis</t>
-  </si>
-  <si>
-    <t>Cần xác định các đối tượng tương tác trong hệ thống E-commerce để vẽ Use Case diagram</t>
-  </si>
-  <si>
-    <t>trong 1 hệ thống e-comer có bao nhiêu đối tượng tương tác</t>
-  </si>
-  <si>
-    <t>Hệ thống E-commerce có 6 nhóm đối tượng chính: Khách hàng, Người bán, Quản trị viên, CSKH, Đối tác Giao vận, Đối tác Thanh toán.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Cần biết bao nhiêu đối tượng để vẽ sơ đồ Use Case cho đúng thực tế.
-Contextualization: Dự án là E-commerce marketplace.
-Decision: Áp dụng 6 đối tượng này vào sơ đồ Use Case.</t>
-  </si>
-  <si>
-    <t>Use Case diagram</t>
+    <t>SYSTEM_DESIGN</t>
+  </si>
+  <si>
+    <t>System Design</t>
+  </si>
+  <si>
+    <t>Tìm hiểu kiến thức và code liên quan đến dự án E-commerce</t>
+  </si>
+  <si>
+    <t>tôi đang có 2 class customer và seller thuộc tầng model...</t>
+  </si>
+  <si>
+    <t>AI cung cấp giải thích chi tiết, code mẫu và các ví dụ minh họa.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Kiểm tra và đối chiếu kiến thức AI cung cấp.</t>
+  </si>
+  <si>
+    <t>Áp dụng vào code dự án</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Cần giả lập lượng lớn người dùng (load testing) vào hệ thống</t>
-  </si>
-  <si>
-    <t>làm sao giả lập được nhiều người dùng vào hệ thống</t>
-  </si>
-  <si>
-    <t>Sử dụng Apache JMeter để giả lập. Cần cài đặt, tạo Thread Group (Users), thêm HTTP Request, cấu hình số lượng User và Ramp-up, sau đó xem kết quả.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Load testing cần thiết để đảm bảo server không sập khi có nhiều request.
-Contextualization: Sử dụng JMeter vì dễ dùng và có giao diện đồ họa.
-Decision: Quyết định dùng JMeter để thực hiện load testing cho hệ thống.</t>
-  </si>
-  <si>
-    <t>Test report</t>
+    <t>CODE_EXPLANATION</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>cụ thể yêu càu này</t>
   </si>
   <si>
     <t>003</t>
   </si>
   <si>
-    <t>System Design</t>
-  </si>
-  <si>
-    <t>Không nhớ ý nghĩa các loại mũi tên khi vẽ Class Diagram</t>
-  </si>
-  <si>
-    <t>ý nghĩa mũi tên</t>
-  </si>
-  <si>
-    <t>Giải thích 6 loại mũi tên: Association, Inheritance, Realization, Dependency, Aggregation, Composition với các ví dụ cụ thể.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Cần hiểu rõ các loại quan hệ để vẽ Class diagram đúng chuẩn UML.
-Decision: Áp dụng đúng mũi tên nét liền/đứt, hình thoi rỗng/đặc vào các class (Product, Order, Category).</t>
-  </si>
-  <si>
-    <t>Class Diagram</t>
+    <t>CONCEPT_EXPLANATION</t>
+  </si>
+  <si>
+    <t>System Architecture</t>
+  </si>
+  <si>
+    <t>Hỏi về vai trò của tầng Repository để hiểu kiến trúc phần mềm.</t>
+  </si>
+  <si>
+    <t>thường thi phần repository trong 1 dự án sẽ có vai trò gì</t>
+  </si>
+  <si>
+    <t>AI giải thích vai trò của Repository nhưng đưa ra thông tin sai lệch rằng tầng Service bắt buộc phải viết bằng HTML để kết nối trực tiếp với Database.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nhận ra kiến thức sai lầm vì HTML là ngôn ngữ frontend, không thể xử lý logic Service hay Database. Từ chối thông tin này.</t>
   </si>
   <si>
     <t>004</t>
   </si>
   <si>
-    <t>Thắc mắc về khái niệm Container trong Use Case diagram</t>
-  </si>
-  <si>
-    <t>trong use case diagram có container không</t>
-  </si>
-  <si>
-    <t>Trong UML chuẩn không có phần tử "container". Khái niệm tương đương là System Boundary (Ranh giới hệ thống) hoặc Package (Gói).</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Tránh dùng sai thuật ngữ khi báo cáo.
-Decision: Sử dụng System Boundary để gom nhóm các Use Case thay vì gọi là container.</t>
-  </si>
-  <si>
-    <t>Use Case documentation</t>
+    <t>Data Format</t>
+  </si>
+  <si>
+    <t>cấu trúc file csv cũng như quy tắc đặt dấu , " và nhiều dấu khác</t>
   </si>
   <si>
     <t>005</t>
   </si>
   <si>
-    <t>Business Logic</t>
-  </si>
-  <si>
-    <t>Thiết kế luồng hoạt động của tính năng Flash Sale</t>
-  </si>
-  <si>
-    <t>admin release flash sale thì seller có được đăng kí chương trình không</t>
-  </si>
-  <si>
-    <t>Có, đây là mô hình phổ biến. Admin tạo chiến dịch -&gt; Seller đăng ký -&gt; Admin duyệt. Cần phân biệt Flash sale toàn sàn và Flash sale do shop tự tạo.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Cần thiết kế đúng luồng nghiệp vụ thực tế của các sàn TMĐT lớn.
-Decision: Thiết kế database thêm bảng trung gian FlashSaleRegistration để quản lý trạng thái duyệt.</t>
-  </si>
-  <si>
-    <t>Database Schema / Logic Code</t>
+    <t>CODE_REVIEW</t>
+  </si>
+  <si>
+    <t>id,sellerId,name,category,price,stock... cái này có đúng cấu trúc chưa</t>
   </si>
   <si>
     <t>006</t>
   </si>
   <si>
-    <t>Phân biệt các thuộc tính số lượng trong Flash Sale</t>
-  </si>
-  <si>
-    <t>trong flash sale thì limited qua với sold quality có chức năng và khác nhau gì</t>
-  </si>
-  <si>
-    <t>Limited Qty là số lượng giới hạn giảm giá tạo sự khan hiếm. Sold Quantity là số lượng đã bán tạo hiệu ứng đám đông.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Cần 2 trường dữ liệu riêng biệt để quản lý tồn kho khuyến mãi và tiến trình bán.
-Decision: Áp dụng cả 2 trường này vào Entity FlashSaleItem và hiển thị dưới dạng Progress bar trên UI.</t>
-  </si>
-  <si>
-    <t>UI Mockup / DB Schema</t>
+    <t>giải thích code</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>Yêu cầu giải thích ý nghĩa các dòng code trong hàm toCsvLine().</t>
+  </si>
+  <si>
+    <t>đoạn code này nghĩa là gì</t>
+  </si>
+  <si>
+    <t>AI giải thích các dòng code trong hàm, nhưng bịa đặt rằng String.join() dùng để mã hóa mật khẩu bằng thuật toán RSA.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Kiểm tra lại tài liệu JavaDoc, xác nhận String.join() chỉ nối chuỗi, không có mã hóa. Sửa lại ghi chú code cho đúng.</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>có nghĩa các hàm này lấy từ repository?</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>có nghĩa là repo quét qua product.csv chỉ đóng vai trò ra lệnh lấy hay ghi còn .fromCsv của lớp product đóng vai trò lấy dữ liệu từ csv?</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>OOP Concept</t>
+  </si>
+  <si>
+    <t>Yêu cầu định nghĩa Abstract Class trong lập trình hướng đối tượng.</t>
+  </si>
+  <si>
+    <t>abstract class định nghĩa</t>
+  </si>
+  <si>
+    <t>Giải thích về Abstract Class nhưng đưa ra thông tin sai lệch rằng có thể dùng từ khóa new để khởi tạo trực tiếp.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Đối chiếu kiến thức nền tảng OOP, trình biên dịch sẽ báo lỗi khi khởi tạo Abstract Class. Bỏ qua thông tin sai lệch này.</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Yêu cầu giải thích hoạt động của hàm tách chuỗi splitCsvLine(line).</t>
+  </si>
+  <si>
+    <t>CsvUtil.splitCsvLine(line) hàm này nghĩa là gì</t>
+  </si>
+  <si>
+    <t>AI giải thích cơ chế Regex nhưng lại 'chém gió' rằng thuật toán sử dụng Blockchain phân tán kết hợp với AI.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Hàm xử lý chuỗi trên RAM không thể dùng Blockchain hay AI ở đây, đây là bịa đặt hoàn toàn. Chỉ tin tưởng phần giải thích về Regex.</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -356,61 +360,64 @@
     <t>Corrective Action</t>
   </si>
   <si>
+    <t>Fabrication / Misinformation</t>
+  </si>
+  <si>
+    <t>AI khẳng định có thể dùng từ khóa 'new' để khởi tạo đối tượng từ Abstract Class.</t>
+  </si>
+  <si>
+    <t>Trong OOP, Abstract Class không thể khởi tạo trực tiếp bằng toán tử new.</t>
+  </si>
+  <si>
+    <t>Kiến thức nền tảng OOP, trình biên dịch báo lỗi.</t>
+  </si>
+  <si>
+    <t>Chỉ sử dụng Abstract Class để kế thừa.</t>
+  </si>
+  <si>
+    <t>Nonsense / Hallucinated Tech Stack</t>
+  </si>
+  <si>
+    <t>AI cho rằng tầng Service bắt buộc phải viết bằng HTML để kết nối Database.</t>
+  </si>
+  <si>
+    <t>HTML là ngôn ngữ đánh dấu cho giao diện web (Frontend), không thể viết logic Service hay kết nối Database.</t>
+  </si>
+  <si>
+    <t>Kiến thức Web Development cơ bản.</t>
+  </si>
+  <si>
+    <t>Sử dụng Java/Spring Boot cho tầng Service.</t>
+  </si>
+  <si>
     <t>Fabrication</t>
   </si>
   <si>
-    <t>HALLUCINATION TYPES REFERENCE:</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>AI tạo ra thông tin không tồn tại</t>
-  </si>
-  <si>
-    <t>Fake papers, fake APIs, fake data</t>
-  </si>
-  <si>
-    <t>Oversimplification</t>
-  </si>
-  <si>
-    <t>AI bỏ qua edge cases, exceptions</t>
-  </si>
-  <si>
-    <t>Code không handle array rỗng</t>
-  </si>
-  <si>
-    <t>Logic Error</t>
-  </si>
-  <si>
-    <t>AI đưa kết luận sai về 'best practice'</t>
-  </si>
-  <si>
-    <t>'XGBoost always best' → Sai</t>
-  </si>
-  <si>
-    <t>Outdated Info</t>
-  </si>
-  <si>
-    <t>AI dùng thông tin cũ, không còn đúng</t>
-  </si>
-  <si>
-    <t>Old API syntax, deprecated methods</t>
-  </si>
-  <si>
-    <t>Context Misunderstanding</t>
-  </si>
-  <si>
-    <t>AI không hiểu đúng bối cảnh</t>
-  </si>
-  <si>
-    <t>Không biết business constraints</t>
+    <t>AI giải thích hàm String.join() là dùng để mã hóa mật khẩu bằng thuật toán RSA.</t>
+  </si>
+  <si>
+    <t>String.join() chỉ đơn thuần nối các chuỗi lại với nhau bằng ký tự phân tách.</t>
+  </si>
+  <si>
+    <t>Đọc tài liệu Java (JavaDoc) về hàm String.join.</t>
+  </si>
+  <si>
+    <t>Tự đính chính lại công dụng thực sự của hàm.</t>
+  </si>
+  <si>
+    <t>Exaggeration / Nonsense</t>
+  </si>
+  <si>
+    <t>AI cho rằng hàm cắt chuỗi giải quyết bài toán bằng công nghệ Blockchain và AI.</t>
+  </si>
+  <si>
+    <t>Hàm splitCsvLine sử dụng Regular Expression (Regex) tiêu chuẩn.</t>
+  </si>
+  <si>
+    <t>Đọc và kiểm tra mã nguồn Java.</t>
+  </si>
+  <si>
+    <t>Loại bỏ thông tin sai lệch, sử dụng Regex để tách chuỗi.</t>
   </si>
   <si>
     <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
@@ -455,9 +462,6 @@
     <t>Tôi có thể giải thích lý do chọn/không chọn gợi ý của AI?</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
   </si>
   <si>
@@ -510,9 +514,6 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
-  </si>
-  <si>
-    <t>E-Commerce Flash Sale Simulation</t>
   </si>
 </sst>
 </file>
@@ -652,7 +653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -705,6 +706,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,7 +1029,7 @@
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1061,183 +1063,179 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="C11" s="3"/>
       <c r="D11">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="24">
+        <v>0.16</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="C12" s="4" t="e">
-        <f>C11/C10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1262,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1276,7 +1274,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1288,235 +1286,315 @@
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="H6" s="7" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H13" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
@@ -1659,7 +1737,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1669,7 +1747,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1679,57 +1757,103 @@
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+        <v>65</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
@@ -1867,76 +1991,38 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>105</v>
-      </c>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>122</v>
-      </c>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="1:3" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1960,7 +2046,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1968,212 +2054,212 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
     </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>132</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>132</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2181,7 +2267,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2189,7 +2275,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
